--- a/Geerts 2023 Figure 4A.xlsx
+++ b/Geerts 2023 Figure 4A.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elber\Documents\git\JSON2SBML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{426D6EF2-8D83-4730-AECB-C3DF6148AC88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CBFAD61B-58C5-46D4-A3A6-D46D51215713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{96608801-79FE-4E93-B95B-7C7EFA946139}"/>
   </bookViews>
